--- a/exercise-library-refresh/exercise-review.xlsx
+++ b/exercise-library-refresh/exercise-review.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -167,6 +167,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2631,34 +2634,34 @@
       <c r="A64" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t>Decline Bench HS</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Decline Bench Press (Hammer Strength)</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Chest</t>
         </is>
       </c>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>Hammer Strength (BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F64" s="21" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED: Hammer Strength category exists on the server but not yet in the Swift app -- see cross-cutting note</t>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Hammer Strength</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Renamed from 'Decline Bench HS'; added 'Press' to match its Barbell/Dumbbell/Smith Machine siblings in this list</t>
         </is>
       </c>
     </row>
@@ -2856,34 +2859,34 @@
       <c r="A71" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t>Dip HS</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Dip (Hammer Strength)</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>Chest</t>
         </is>
       </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>Hammer Strength (BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F71" s="21" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="G71" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED: Hammer Strength -- see cross-cutting note. Body part guessed as Chest</t>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Hammer Strength</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Renamed from 'Dip HS'</t>
         </is>
       </c>
     </row>
@@ -3516,34 +3519,34 @@
       <c r="A91" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t>HS Bench Press</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Bench Press (Hammer Strength)</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>Chest</t>
         </is>
       </c>
-      <c r="D91" s="10" t="inlineStr">
-        <is>
-          <t>Hammer Strength (BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E91" s="10" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F91" s="21" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="G91" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED: Hammer Strength -- see cross-cutting note</t>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Hammer Strength</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Renamed from 'HS Bench Press' -- Drake's own naming example</t>
         </is>
       </c>
     </row>
@@ -3551,34 +3554,34 @@
       <c r="A92" s="10" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="11" t="inlineStr">
-        <is>
-          <t>HS ISO Lat Pull Down</t>
-        </is>
-      </c>
-      <c r="C92" s="10" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Lat Pulldown (Hammer Strength)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="D92" s="10" t="inlineStr">
-        <is>
-          <t>Hammer Strength (BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E92" s="10" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F92" s="21" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="G92" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED: Hammer Strength -- see cross-cutting note</t>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Hammer Strength</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Renamed from 'HS ISO Lat Pull Down'. Dropped 'ISO' as redundant with '(Hammer Strength)' -- but the real machine is typically single-arm/independent, so if that distinction matters to you, consider 'Lat Pulldown - Single Arm (Hammer Strength)' instead</t>
         </is>
       </c>
     </row>
@@ -3586,34 +3589,34 @@
       <c r="A93" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t>HS Incline Bench Press</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Incline Bench Press (Hammer Strength)</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>Chest</t>
         </is>
       </c>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>Hammer Strength (BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E93" s="10" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F93" s="21" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="G93" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED: Hammer Strength -- see cross-cutting note</t>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Hammer Strength</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Renamed from 'HS Incline Bench Press'</t>
         </is>
       </c>
     </row>
@@ -3621,34 +3624,34 @@
       <c r="A94" s="10" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t>HS Incline Chest Fly</t>
-        </is>
-      </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Incline Chest Fly (Hammer Strength)</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>Chest</t>
         </is>
       </c>
-      <c r="D94" s="10" t="inlineStr">
-        <is>
-          <t>Hammer Strength (BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E94" s="10" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F94" s="21" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="G94" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED: Hammer Strength -- see cross-cutting note</t>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Hammer Strength</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Renamed from 'HS Incline Chest Fly'</t>
         </is>
       </c>
     </row>
@@ -3656,34 +3659,34 @@
       <c r="A95" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="11" t="inlineStr">
-        <is>
-          <t>HS Seated Low Row</t>
-        </is>
-      </c>
-      <c r="C95" s="10" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Seated Low Row (Hammer Strength)</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>Hammer Strength (BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E95" s="10" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F95" s="21" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="G95" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED: Hammer Strength -- see cross-cutting note</t>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Hammer Strength</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Renamed from 'HS Seated Low Row'</t>
         </is>
       </c>
     </row>
@@ -3691,34 +3694,34 @@
       <c r="A96" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="11" t="inlineStr">
-        <is>
-          <t>HS Shoulder Press</t>
-        </is>
-      </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Shoulder Press (Hammer Strength)</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>Shoulders</t>
         </is>
       </c>
-      <c r="D96" s="10" t="inlineStr">
-        <is>
-          <t>Hammer Strength (BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E96" s="10" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F96" s="21" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="G96" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED: Hammer Strength -- see cross-cutting note</t>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Hammer Strength</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Renamed from 'HS Shoulder Press'</t>
         </is>
       </c>
     </row>
@@ -3726,34 +3729,34 @@
       <c r="A97" s="10" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t>HS Single Arm Row</t>
-        </is>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Single Arm Row (Hammer Strength)</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="D97" s="10" t="inlineStr">
-        <is>
-          <t>Hammer Strength (BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E97" s="10" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F97" s="21" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="G97" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED: Hammer Strength -- see cross-cutting note</t>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Hammer Strength</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Renamed from 'HS Single Arm Row'</t>
         </is>
       </c>
     </row>
@@ -4797,34 +4800,34 @@
       <c r="A130" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>Iso-Lateral Chest Press (Machine)</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Chest Press (Hammer Strength)</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>Chest</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>Machine</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="F130" s="21" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="G130" s="7" t="inlineStr">
-        <is>
-          <t>'Iso-Lateral' is Hammer Strength's own branding term -- is this actually the same as the 'HS' rows? Please confirm</t>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Hammer Strength</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Renamed from 'Iso-Lateral Chest Press (Machine)' -- confirmed as Hammer Strength 2026-08-19</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4835,34 @@
       <c r="A131" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>Iso-Lateral Row (Machine)</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Row (Hammer Strength)</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>Machine</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="F131" s="21" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="G131" s="7" t="inlineStr">
-        <is>
-          <t>Same question as #129</t>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Hammer Strength</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Renamed from 'Iso-Lateral Row (Machine)' -- confirmed as Hammer Strength 2026-08-19. Fairly generic against #94 Seated Low Row and #96 Single Arm Row (Hammer Strength) -- worth a look at whether this is actually one of those two under yet another name</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10774,6 @@
       </c>
       <c r="G311" s="5" t="inlineStr"/>
     </row>
-    <row r="312"/>
     <row r="313">
       <c r="A313" s="12" t="inlineStr">
         <is>
@@ -10833,7 +10835,7 @@
       <formula1>"Arms,Back,Cardio,Chest,Core,Full Body,Legs,Olympic,Other,Shoulders"</formula1>
     </dataValidation>
     <dataValidation sqref="D2 D3 D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D68 D69 D70 D71 D72 D73 D74 D75 D76 D77 D78 D79 D80 D81 D82 D83 D84 D85 D86 D87 D88 D89 D90 D91 D92 D93 D94 D95 D96 D97 D98 D99 D100 D101 D102 D103 D104 D105 D106 D107 D108 D109 D110 D111 D112 D113 D114 D115 D116 D117 D118 D119 D120 D121 D122 D123 D124 D125 D126 D127 D128 D129 D130 D131 D132 D133 D134 D135 D136 D137 D138 D139 D140 D141 D142 D143 D144 D145 D146 D147 D148 D149 D150 D151 D152 D153 D154 D155 D156 D157 D158 D159 D160 D161 D162 D163 D164 D165 D166 D167 D168 D169 D170 D171 D172 D173 D174 D175 D176 D177 D178 D179 D180 D181 D182 D183 D184 D185 D186 D187 D188 D189 D190 D191 D192 D193 D194 D195 D196 D197 D198 D199 D200 D201 D202 D203 D204 D205 D206 D207 D208 D209 D210 D211 D212 D213 D214 D215 D216 D217 D218 D219 D220 D221 D222 D223 D224 D225 D226 D227 D228 D229 D230 D231 D232 D233 D234 D235 D236 D237 D238 D239 D240 D241 D242 D243 D244 D245 D246 D247 D248 D249 D250 D251 D252 D253 D254 D255 D256 D257 D258 D259 D260 D261 D262 D263 D264 D265 D266 D267 D268 D269 D270 D271 D272 D273 D274 D275 D276 D277 D278 D279 D280 D281 D282 D283 D284 D285 D286 D287 D288 D289 D290 D291 D292 D293 D294 D295 D296 D297 D298 D299 D300 D301 D302 D303 D304 D305 D306 D307 D308 D309 D310 D311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Barbell,Dumbbell,Machine,Weighted Bodyweight,Assisted Bodyweight,Reps Only,Cardio,Duration,Hammer Strength (BLOCKED)"</formula1>
+      <formula1>"Barbell,Dumbbell,Machine,Weighted Bodyweight,Assisted Bodyweight,Reps Only,Cardio,Duration,Hammer Strength"</formula1>
     </dataValidation>
     <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F119 F120 F121 F122 F123 F124 F125 F126 F127 F128 F129 F130 F131 F132 F133 F134 F135 F136 F137 F138 F139 F140 F141 F142 F143 F144 F145 F146 F147 F148 F149 F150 F151 F152 F153 F154 F155 F156 F157 F158 F159 F160 F161 F162 F163 F164 F165 F166 F167 F168 F169 F170 F171 F172 F173 F174 F175 F176 F177 F178 F179 F180 F181 F182 F183 F184 F185 F186 F187 F188 F189 F190 F191 F192 F193 F194 F195 F196 F197 F198 F199 F200 F201 F202 F203 F204 F205 F206 F207 F208 F209 F210 F211 F212 F213 F214 F215 F216 F217 F218 F219 F220 F221 F222 F223 F224 F225 F226 F227 F228 F229 F230 F231 F232 F233 F234 F235 F236 F237 F238 F239 F240 F241 F242 F243 F244 F245 F246 F247 F248 F249 F250 F251 F252 F253 F254 F255 F256 F257 F258 F259 F260 F261 F262 F263 F264 F265 F266 F267 F268 F269 F270 F271 F272 F273 F274 F275 F276 F277 F278 F279 F280 F281 F282 F283 F284 F285 F286 F287 F288 F289 F290 F291 F292 F293 F294 F295 F296 F297 F298 F299 F300 F301 F302 F303 F304 F305 F306 F307 F308 F309 F310 F311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Arms,Back,Cardio,Chest,Core,Full Body,Legs,Olympic,Other,Shoulders,(none)"</formula1>
@@ -10869,26 +10871,26 @@
       </c>
     </row>
     <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>Hammer Strength category is BLOCKED in the app today</t>
-        </is>
-      </c>
-      <c r="B2" s="20" t="inlineStr">
-        <is>
-          <t>Postgres already has the workout_calorie_rate-style enum public.hammer_strength added, but the Swift ExerciseCategory enum has no matching case yet -- it's a static string constant, not a real case, specifically so nothing could seed it by accident. 9 rows in this list (#63, #70, #90-96) need it. Two options: (1) I add the Swift case now -- a small, mechanical change (one enum case + one line in an exhaustive switch) -- and these 9 exercises seed correctly, or (2) file them as Machine for now and revisit later. Your call.</t>
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-08-19 -- Hammer Strength category is unblocked</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Was blocked by a small gap in the app's code (Postgres and the AI server both already supported it). Fixed: the app now has a real Hammer Strength category. All 9 'HS'-named rows are retagged and renamed to match this list's own naming pattern -- e.g. 'HS Bench Press' -&gt; 'Bench Press (Hammer Strength)'. Nothing else to decide here.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>'Iso-Lateral' machines -- same brand as 'HS'?</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>#129 and #130 use 'Iso-Lateral', which is Hammer Strength's own branding for its plate-loaded machines. If these are the same equipment as the 'HS ___' rows, they should also be tagged Hammer Strength once that category exists. Currently filed as Machine, pending your answer.</t>
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-08-19 -- 'Iso-Lateral' machines confirmed as Hammer Strength</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>#129 and #130 (now 'Chest Press (Hammer Strength)' and 'Row (Hammer Strength)') are tagged Hammer Strength, same as the 9 'HS'-named rows. #130 is worth a second look -- 'Row (Hammer Strength)' is fairly generic against #94 Seated Low Row and #96 Single Arm Row, also Hammer Strength; it may be the same machine under a third name.</t>
         </is>
       </c>
     </row>
